--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_440_Lithuania.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_440_Lithuania.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rd111fd5144204287"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R0dc6e50474974607"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R4b34537a7a69416a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R40efdbc428764b02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R903ce576cb7d4469"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R4bb08f078c3c4740"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R94134858bd6444b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rc89327a717264cd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R0f82c50081054fc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R1200f06c9a714158"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rcfbfd266cdb543c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rad2a37ccb64c45ae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ440CommercialTable" displayName="EEZ440CommercialTable" ref="A1:O8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O8"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ440CommercialTable" displayName="EEZ440CommercialTable" ref="A1:E8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E8"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ440FunctionalTable" displayName="EEZ440FunctionalTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ440FunctionalTable" displayName="EEZ440FunctionalTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ440ValidationTable" displayName="EEZ440ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ440ValidationTable" displayName="EEZ440ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -3575,7 +3529,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa1c1c0d40844d2f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac45c1dc6c5d4aeb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3585,20 +3539,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -3606,444 +3550,155 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>4058.2180933856</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.0898169030286615</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1229.750203301519</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>4058.2180933856</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1229.8744254907251</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$44,A2,'Species'!$U$2:$U$44))</x:f>
-        <x:v>4991098.64611868</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.0898169030286615</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1229.750203301519</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>4990594.525382844</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>504.1207358362153</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0001010141643991</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.00010101416439908884</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>965.4720293821999</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.4808348228862567</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>302.5762407820587</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>965.4720293821999</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>341.14087042811286</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$44,A3,'Species'!$U$2:$U$44))</x:f>
-        <x:v>329361.96847744024</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.4808348228862567</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>302.5762407820587</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>292128.89723069133</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>37233.07124674891</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.12745425597984</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.12745425597984</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>28895.6401566192</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.125240364321362</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>133.4259686284007</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>28895.6401566192</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>145.3561243820489</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$44,A4,'Species'!$U$2:$U$44))</x:f>
-        <x:v>4200158.264704468</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.125240364321362</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>133.4259686284007</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>3855428.777034629</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>344729.4876698386</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0894140464280564</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.08941404642805628</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>426.82161353429996</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.0284019943679836</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>106.75838476489061</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>426.82161353429996</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>182.69820515209133</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$44,A5,'Species'!$U$2:$U$44))</x:f>
-        <x:v>77979.54271283618</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.0284019943679836</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>106.75838476489061</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>45566.78604366624</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>32412.75666916994</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.7113241789339517</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.7113241789339517</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>232.2753838485</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.65592183960306</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>452.8160788233185</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>232.2753838485</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>836.3962796612466</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$44,A6,'Species'!$U$2:$U$44))</x:f>
-        <x:v>194274.26690777342</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.65592183960306</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>452.8160788233185</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>105178.02852145894</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>89096.23838631448</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.8470993385100067</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.8470993385100066</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>129.1324388278</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.4799365470551833</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>301.95105201570675</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>129.1324388278</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>347.8753989971257</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$44,A7,'Species'!$U$2:$U$44))</x:f>
-        <x:v>44921.99868069286</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.4799365470551833</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>301.95105201570675</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>38991.67575340811</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>5930.322927284746</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.152092025097598</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.1520920250975979</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>0.0019755545</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.69</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>489.77881936844614</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>0.0019755545</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>489.77881936844614</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$44,A8,'Species'!$U$2:$U$44))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>0.9675847506080211</x:v>
       </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.69</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>489.77881936844614</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>0.9675847506080211</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G8">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O8">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R012fde8bd8e64f9e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bb09fcd3abe49a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4053,20 +3708,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4074,714 +3719,250 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>4057.6117400406997</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.090233751582038</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1230.931120183967</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>4057.6117400406997</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1231.3823401664506</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$44,A2,'Species'!$U$2:$U$44))</x:f>
-        <x:v>4996471.43993818</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.090233751582038</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1230.931120183967</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>4994640.564439914</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1830.8754982659593</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0003665680191887</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0003665680191886378</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>18.271460713000007</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.6502198917807447</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>446.9098140457146</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>18.271460713000007</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>493.05023589545885</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$44,A3,'Species'!$U$2:$U$44))</x:f>
-        <x:v>9008.748014699262</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.6502198917807447</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>446.9098140457146</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>8165.695109590413</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>843.0529051088488</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1032432504268623</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.10324325042686242</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>5.2747007987</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.3476939371639824</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2226.8652446614947</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>5.2747007987</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2267.2747200649733</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$44,A4,'Species'!$U$2:$U$44))</x:f>
-        <x:v>11959.195776799033</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.3476939371639824</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2226.8652446614947</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>11746.047884613256</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>213.1478921857779</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.018146349672641</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.018146349672641053</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>87.66285175680001</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.9733166667672486</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>940.4087617317205</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>87.66285175680001</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1011.4185611024528</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$44,A5,'Species'!$U$2:$U$44))</x:f>
-        <x:v>88663.8353860003</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.9733166667672486</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>940.4087617317205</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>82438.91387048367</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>6224.921515516631</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0755095042287475</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.07550950422874743</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>60.2935586092</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.9593179490264037</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>91.05796683112365</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>60.2935586092</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>91.07004611210064</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$44,A6,'Species'!$U$2:$U$44))</x:f>
-        <x:v>5490.9371628024865</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.9593179490264037</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>91.05796683112365</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>5490.208859966943</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0.728302835543218</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0001326548505018</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.00013265485050191754</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>309.14839355090004</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.0532153830263526</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>113.03563620739169</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>309.14839355090004</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>367.14423875161054</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$44,A7,'Species'!$U$2:$U$44))</x:f>
-        <x:v>113502.0516115285</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.0532153830263526</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>113.03563620739169</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>34944.78534751909</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>78557.2662640094</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>3.2480397427762875</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>2.2480397427762875</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>9190.851501938601</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.3832449495393493</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>241.68235800694924</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>9190.851501938601</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>244.15852496738023</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$44,A8,'Species'!$U$2:$U$44))</x:f>
-        <x:v>2244024.74590756</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.3832449495393493</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>241.68235800694924</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>2221266.663080232</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>22758.082827327773</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0102455428722679</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.010245542872267808</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>0.4857988577</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.31</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>204.17379446695296</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>0.4857988577</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$44,A9,'Species'!$U$2:$U$44))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>99.18739612432032</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.31</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>99.18739612432032</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>7.5862104404</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.087963559989619</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>122.45134506537559</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>7.5862104404</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>123.16974768077212</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$44,A10,'Species'!$U$2:$U$44))</x:f>
-        <x:v>934.3916257973071</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.087963559989619</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>122.45134506537559</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>928.9416723759754</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>5.44995342133177</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0058668413565648</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.005866841356564723</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>19911.6396315782</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.01</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>102.32929922807536</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>19911.6396315782</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>102.32929922807536</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$44,A11,'Species'!$U$2:$U$44))</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>2037544.1299813697</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.01</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>102.32929922807536</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
-        <x:v>2037544.1299813697</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>98.5385142844</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.1099999999999994</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>128.82495516931323</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>98.5385142844</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$44,A12,'Species'!$U$2:$U$44))</x:f>
-        <x:v>12694.219685138574</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.1099999999999994</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>128.82495516931323</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>12694.21968513856</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1.4551915228366852e-11</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>1.146341846076852e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>960.1973285834999</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.4760728616452417</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>299.2766691373478</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>960.1973285834999</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>330.55994143295464</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$44,A13,'Species'!$U$2:$U$44))</x:f>
-        <x:v>317402.77270064125</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.4760728616452417</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>299.2766691373478</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>287364.65821304935</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>30038.114487591898</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.1045296059521763</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.10452960595217639</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7688bcc063a24e09"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R323adda853bd40af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4956,7 +4137,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -5055,7 +4236,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>9837795.655186638</x:v>
+        <x:v>9327889.657551447</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5069,7 +4250,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>9837795.655186642</x:v>
+        <x:v>9697324.015540378</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5083,7 +4264,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-1.862645149230957e-9</x:v>
+        <x:v>-509905.99763519317</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5097,7 +4278,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>1.862645149230957e-9</x:v>
+        <x:v>-140471.63964626193</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5108,9 +4289,9 @@
         <x:v>EEZ_440</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -5122,47 +4303,19 @@
         <x:v>EEZ_440</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_440</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_440</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd905a5648b654148"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1e55f3c2ce74328"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5209,7 +4362,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
